--- a/EktaTrust/Files/BibData/BibData.xlsx
+++ b/EktaTrust/Files/BibData/BibData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Development\Projects\EktaTrust\Latest-Code\Ekta-trust\EktaTrust\Files\BibData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEC0F4E-D33D-488D-B9FB-3F458CD85E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="22149" windowHeight="12549"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4199" uniqueCount="1288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4940" uniqueCount="1354">
   <si>
     <t>Category Name</t>
   </si>
@@ -3883,13 +3889,211 @@
   </si>
   <si>
     <t>Venue to Collect BIB</t>
+  </si>
+  <si>
+    <t>DUN9283158</t>
+  </si>
+  <si>
+    <t>DUN9286255</t>
+  </si>
+  <si>
+    <t>DUN9291146</t>
+  </si>
+  <si>
+    <t>DUN9291981</t>
+  </si>
+  <si>
+    <t>DUN9613002</t>
+  </si>
+  <si>
+    <t>DUN9623648</t>
+  </si>
+  <si>
+    <t>DUN9634241</t>
+  </si>
+  <si>
+    <t>JRC1326</t>
+  </si>
+  <si>
+    <t>JRC1508</t>
+  </si>
+  <si>
+    <t>JRC1648</t>
+  </si>
+  <si>
+    <t>JRC1646</t>
+  </si>
+  <si>
+    <t>JRC1385</t>
+  </si>
+  <si>
+    <t>JRC1700</t>
+  </si>
+  <si>
+    <t>JRC1768</t>
+  </si>
+  <si>
+    <t>JRC1235</t>
+  </si>
+  <si>
+    <t>JRC1266</t>
+  </si>
+  <si>
+    <t>JRC1370</t>
+  </si>
+  <si>
+    <t>JRC1240</t>
+  </si>
+  <si>
+    <t>JRC1222</t>
+  </si>
+  <si>
+    <t>JRC1184</t>
+  </si>
+  <si>
+    <t>JRC1575</t>
+  </si>
+  <si>
+    <t>JRC1124</t>
+  </si>
+  <si>
+    <t>JRC1682</t>
+  </si>
+  <si>
+    <t>JRC1559</t>
+  </si>
+  <si>
+    <t>JRC1524</t>
+  </si>
+  <si>
+    <t>AMB2</t>
+  </si>
+  <si>
+    <t>AMB3</t>
+  </si>
+  <si>
+    <t>AMB4</t>
+  </si>
+  <si>
+    <t>AMB5</t>
+  </si>
+  <si>
+    <t>AMB6</t>
+  </si>
+  <si>
+    <t>PRC106</t>
+  </si>
+  <si>
+    <t>PRC108</t>
+  </si>
+  <si>
+    <t>PRC110</t>
+  </si>
+  <si>
+    <t>PRC116</t>
+  </si>
+  <si>
+    <t>PRC117</t>
+  </si>
+  <si>
+    <t>PRC121</t>
+  </si>
+  <si>
+    <t>PRC127</t>
+  </si>
+  <si>
+    <t>PRC128</t>
+  </si>
+  <si>
+    <t>PRC138</t>
+  </si>
+  <si>
+    <t>PRC142</t>
+  </si>
+  <si>
+    <t>PRC150</t>
+  </si>
+  <si>
+    <t>PRC151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shashi Kiran </t>
+  </si>
+  <si>
+    <t>KRISHAN DUTT SHARMA</t>
+  </si>
+  <si>
+    <t>Dr Sukesh Jakhar</t>
+  </si>
+  <si>
+    <t>Saurabh Kumar Soni</t>
+  </si>
+  <si>
+    <t>LALIT PARIS</t>
+  </si>
+  <si>
+    <t>Harshwardhan Singh</t>
+  </si>
+  <si>
+    <t>Dharmendra jain</t>
+  </si>
+  <si>
+    <t>Suraj Meena</t>
+  </si>
+  <si>
+    <t>Mahesh Dewidi</t>
+  </si>
+  <si>
+    <t>Dr. Namit Sharma</t>
+  </si>
+  <si>
+    <t>Prem Raj Jogpal</t>
+  </si>
+  <si>
+    <t>Renu Singh</t>
+  </si>
+  <si>
+    <t>Dr sukesh jakhar</t>
+  </si>
+  <si>
+    <t>Sunil Kumawat</t>
+  </si>
+  <si>
+    <t>Srizan dwivedi</t>
+  </si>
+  <si>
+    <t>MALE</t>
+  </si>
+  <si>
+    <t>shashi_monty@yahoo.com</t>
+  </si>
+  <si>
+    <t>saurabhsoni.mech@mnit.ac.in</t>
+  </si>
+  <si>
+    <t>paris.lalit97@gmail.com</t>
+  </si>
+  <si>
+    <t>SUNILGEORGIAN1888@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>harshwork1407@gmail.com</t>
+  </si>
+  <si>
+    <t>jain.dharmendra@gmail.com</t>
+  </si>
+  <si>
+    <t>sunilkumawatn@gmail.com</t>
+  </si>
+  <si>
+    <t>coachvj2009@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3903,6 +4107,14 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3922,19 +4134,34 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink 2" xfId="1"/>
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4239,38 +4466,38 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S526"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S636"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.15234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.84375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.53515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.53515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.84375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.15234375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="34.3828125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.15234375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.3046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.3828125" customWidth="1"/>
-    <col min="19" max="19" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.42578125" customWidth="1"/>
+    <col min="19" max="19" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4329,7 +4556,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -4379,7 +4606,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -4429,7 +4656,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -4479,7 +4706,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -4529,7 +4756,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -4579,7 +4806,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -4632,7 +4859,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -4682,7 +4909,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -4732,7 +4959,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -4782,7 +5009,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -4832,7 +5059,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -4882,7 +5109,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -4935,7 +5162,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -4985,7 +5212,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -5035,7 +5262,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -5085,7 +5312,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -5138,7 +5365,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -5191,7 +5418,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -5244,7 +5471,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -5297,7 +5524,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -5347,7 +5574,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -5397,7 +5624,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -5450,7 +5677,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -5500,7 +5727,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -5550,7 +5777,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -5600,7 +5827,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -5650,7 +5877,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -5700,7 +5927,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -5750,7 +5977,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -5803,7 +6030,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -5853,7 +6080,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -5903,7 +6130,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -5953,7 +6180,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -6003,7 +6230,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -6056,7 +6283,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -6106,7 +6333,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -6159,7 +6386,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -6209,7 +6436,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -6259,7 +6486,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -6309,7 +6536,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -6359,7 +6586,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -6409,7 +6636,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -6459,7 +6686,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -6509,7 +6736,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -6559,7 +6786,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -6609,7 +6836,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -6662,7 +6889,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -6712,7 +6939,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -6762,7 +6989,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -6812,7 +7039,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -6862,7 +7089,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -6912,7 +7139,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -6962,7 +7189,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -7015,7 +7242,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -7065,7 +7292,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -7118,7 +7345,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -7171,7 +7398,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -7221,7 +7448,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -7271,7 +7498,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -7321,7 +7548,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -7371,7 +7598,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -7421,7 +7648,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -7471,7 +7698,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -7524,7 +7751,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -7574,7 +7801,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -7624,7 +7851,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -7674,7 +7901,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -7724,7 +7951,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -7774,7 +8001,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -7824,7 +8051,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -7874,7 +8101,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -7924,7 +8151,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -7974,7 +8201,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -8024,7 +8251,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -8074,7 +8301,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -8127,7 +8354,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -8180,7 +8407,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -8230,7 +8457,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>17</v>
       </c>
@@ -8280,7 +8507,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -8330,7 +8557,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>17</v>
       </c>
@@ -8383,7 +8610,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>17</v>
       </c>
@@ -8436,7 +8663,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>17</v>
       </c>
@@ -8486,7 +8713,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>17</v>
       </c>
@@ -8539,7 +8766,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -8589,7 +8816,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>17</v>
       </c>
@@ -8639,7 +8866,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -8689,7 +8916,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -8742,7 +8969,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -8792,7 +9019,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -8842,7 +9069,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>17</v>
       </c>
@@ -8895,7 +9122,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -8948,7 +9175,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>17</v>
       </c>
@@ -9001,7 +9228,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -9051,7 +9278,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>17</v>
       </c>
@@ -9104,7 +9331,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -9154,7 +9381,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -9204,7 +9431,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -9254,7 +9481,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -9304,7 +9531,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -9354,7 +9581,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -9407,7 +9634,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -9457,7 +9684,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -9507,7 +9734,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>17</v>
       </c>
@@ -9557,7 +9784,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>17</v>
       </c>
@@ -9607,7 +9834,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -9657,7 +9884,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -9707,7 +9934,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -9757,7 +9984,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -9807,7 +10034,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -9857,7 +10084,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -9910,7 +10137,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>17</v>
       </c>
@@ -9960,7 +10187,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>17</v>
       </c>
@@ -10013,7 +10240,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>17</v>
       </c>
@@ -10063,7 +10290,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -10116,7 +10343,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>17</v>
       </c>
@@ -10169,7 +10396,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>17</v>
       </c>
@@ -10219,7 +10446,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>17</v>
       </c>
@@ -10269,7 +10496,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>17</v>
       </c>
@@ -10319,7 +10546,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>17</v>
       </c>
@@ -10369,7 +10596,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>17</v>
       </c>
@@ -10419,7 +10646,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>17</v>
       </c>
@@ -10472,7 +10699,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>17</v>
       </c>
@@ -10525,7 +10752,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>17</v>
       </c>
@@ -10575,7 +10802,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>17</v>
       </c>
@@ -10628,7 +10855,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>17</v>
       </c>
@@ -10678,7 +10905,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>17</v>
       </c>
@@ -10731,7 +10958,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>17</v>
       </c>
@@ -10781,7 +11008,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>17</v>
       </c>
@@ -10831,7 +11058,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>17</v>
       </c>
@@ -10881,7 +11108,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>17</v>
       </c>
@@ -10931,7 +11158,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>17</v>
       </c>
@@ -10981,7 +11208,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>17</v>
       </c>
@@ -11031,7 +11258,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>17</v>
       </c>
@@ -11081,7 +11308,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>17</v>
       </c>
@@ -11131,7 +11358,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>17</v>
       </c>
@@ -11181,7 +11408,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>17</v>
       </c>
@@ -11231,7 +11458,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>17</v>
       </c>
@@ -11281,7 +11508,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>17</v>
       </c>
@@ -11331,7 +11558,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>17</v>
       </c>
@@ -11381,7 +11608,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>17</v>
       </c>
@@ -11431,7 +11658,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>17</v>
       </c>
@@ -11484,7 +11711,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>17</v>
       </c>
@@ -11534,7 +11761,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>17</v>
       </c>
@@ -11587,7 +11814,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>17</v>
       </c>
@@ -11637,7 +11864,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>17</v>
       </c>
@@ -11687,7 +11914,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>17</v>
       </c>
@@ -11737,7 +11964,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -11787,7 +12014,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>17</v>
       </c>
@@ -11837,7 +12064,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>17</v>
       </c>
@@ -11890,7 +12117,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>17</v>
       </c>
@@ -11940,7 +12167,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>17</v>
       </c>
@@ -11990,7 +12217,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>17</v>
       </c>
@@ -12040,7 +12267,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>17</v>
       </c>
@@ -12090,7 +12317,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>17</v>
       </c>
@@ -12140,7 +12367,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>17</v>
       </c>
@@ -12190,7 +12417,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>17</v>
       </c>
@@ -12240,7 +12467,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>17</v>
       </c>
@@ -12293,7 +12520,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>17</v>
       </c>
@@ -12343,7 +12570,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>17</v>
       </c>
@@ -12393,7 +12620,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>17</v>
       </c>
@@ -12443,7 +12670,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>17</v>
       </c>
@@ -12493,7 +12720,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>17</v>
       </c>
@@ -12546,7 +12773,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>17</v>
       </c>
@@ -12596,7 +12823,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>17</v>
       </c>
@@ -12649,7 +12876,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>17</v>
       </c>
@@ -12702,7 +12929,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>17</v>
       </c>
@@ -12752,7 +12979,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>17</v>
       </c>
@@ -12802,7 +13029,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>17</v>
       </c>
@@ -12852,7 +13079,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>17</v>
       </c>
@@ -12905,7 +13132,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>17</v>
       </c>
@@ -12958,7 +13185,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>17</v>
       </c>
@@ -13008,7 +13235,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>17</v>
       </c>
@@ -13058,7 +13285,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>17</v>
       </c>
@@ -13111,7 +13338,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -13161,7 +13388,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>17</v>
       </c>
@@ -13214,7 +13441,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>17</v>
       </c>
@@ -13264,7 +13491,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>17</v>
       </c>
@@ -13314,7 +13541,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>17</v>
       </c>
@@ -13367,7 +13594,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>17</v>
       </c>
@@ -13417,7 +13644,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>17</v>
       </c>
@@ -13467,7 +13694,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>17</v>
       </c>
@@ -13517,7 +13744,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>17</v>
       </c>
@@ -13567,7 +13794,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>17</v>
       </c>
@@ -13620,7 +13847,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>17</v>
       </c>
@@ -13670,7 +13897,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>17</v>
       </c>
@@ -13720,7 +13947,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>17</v>
       </c>
@@ -13770,7 +13997,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>17</v>
       </c>
@@ -13823,7 +14050,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>17</v>
       </c>
@@ -13873,7 +14100,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>17</v>
       </c>
@@ -13923,7 +14150,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>17</v>
       </c>
@@ -13973,7 +14200,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>17</v>
       </c>
@@ -14026,7 +14253,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>17</v>
       </c>
@@ -14076,7 +14303,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -14129,7 +14356,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -14179,7 +14406,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>17</v>
       </c>
@@ -14229,7 +14456,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>17</v>
       </c>
@@ -14279,7 +14506,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>17</v>
       </c>
@@ -14329,7 +14556,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>17</v>
       </c>
@@ -14382,7 +14609,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
         <v>716</v>
       </c>
@@ -14414,7 +14641,7 @@
         <v>9782346168</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
         <v>716</v>
       </c>
@@ -14446,7 +14673,7 @@
         <v>8209021211</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
         <v>716</v>
       </c>
@@ -14478,7 +14705,7 @@
         <v>7737021146</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
         <v>716</v>
       </c>
@@ -14510,7 +14737,7 @@
         <v>9214328923</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
         <v>716</v>
       </c>
@@ -14542,7 +14769,7 @@
         <v>9799973035</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
         <v>716</v>
       </c>
@@ -14574,7 +14801,7 @@
         <v>9602704050</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
         <v>716</v>
       </c>
@@ -14606,7 +14833,7 @@
         <v>6378680304</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>716</v>
       </c>
@@ -14638,7 +14865,7 @@
         <v>8005778291</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
         <v>716</v>
       </c>
@@ -14670,7 +14897,7 @@
         <v>6378680304</v>
       </c>
     </row>
-    <row r="209" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="209" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
         <v>716</v>
       </c>
@@ -14702,7 +14929,7 @@
         <v>9413000123</v>
       </c>
     </row>
-    <row r="210" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="210" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
         <v>716</v>
       </c>
@@ -14734,7 +14961,7 @@
         <v>9829005945</v>
       </c>
     </row>
-    <row r="211" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="211" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
         <v>716</v>
       </c>
@@ -14766,7 +14993,7 @@
         <v>9602704050</v>
       </c>
     </row>
-    <row r="212" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="212" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
         <v>716</v>
       </c>
@@ -14798,7 +15025,7 @@
         <v>6350579146</v>
       </c>
     </row>
-    <row r="213" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="213" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
         <v>716</v>
       </c>
@@ -14830,7 +15057,7 @@
         <v>7976872733</v>
       </c>
     </row>
-    <row r="214" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="214" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
         <v>716</v>
       </c>
@@ -14862,7 +15089,7 @@
         <v>9460484849</v>
       </c>
     </row>
-    <row r="215" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="215" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
         <v>716</v>
       </c>
@@ -14891,7 +15118,7 @@
         <v>9460484849</v>
       </c>
     </row>
-    <row r="216" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="216" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
         <v>716</v>
       </c>
@@ -14923,7 +15150,7 @@
         <v>9460974100</v>
       </c>
     </row>
-    <row r="217" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="217" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
         <v>716</v>
       </c>
@@ -14955,7 +15182,7 @@
         <v>9460974100</v>
       </c>
     </row>
-    <row r="218" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="218" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
         <v>716</v>
       </c>
@@ -14987,7 +15214,7 @@
         <v>9460974100</v>
       </c>
     </row>
-    <row r="219" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="219" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
         <v>716</v>
       </c>
@@ -15019,7 +15246,7 @@
         <v>9460974100</v>
       </c>
     </row>
-    <row r="220" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="220" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
         <v>716</v>
       </c>
@@ -15051,7 +15278,7 @@
         <v>9460974100</v>
       </c>
     </row>
-    <row r="221" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="221" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
         <v>716</v>
       </c>
@@ -15083,7 +15310,7 @@
         <v>9413000123</v>
       </c>
     </row>
-    <row r="222" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="222" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
         <v>716</v>
       </c>
@@ -15115,7 +15342,7 @@
         <v>9982712732</v>
       </c>
     </row>
-    <row r="223" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="223" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
         <v>716</v>
       </c>
@@ -15147,7 +15374,7 @@
         <v>8076555131</v>
       </c>
     </row>
-    <row r="224" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="224" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
         <v>716</v>
       </c>
@@ -15179,7 +15406,7 @@
         <v>9785468700</v>
       </c>
     </row>
-    <row r="225" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="225" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
         <v>716</v>
       </c>
@@ -15211,7 +15438,7 @@
         <v>7339827175</v>
       </c>
     </row>
-    <row r="226" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="226" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
         <v>716</v>
       </c>
@@ -15243,7 +15470,7 @@
         <v>9636659752</v>
       </c>
     </row>
-    <row r="227" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="227" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
         <v>716</v>
       </c>
@@ -15275,7 +15502,7 @@
         <v>6378161523</v>
       </c>
     </row>
-    <row r="228" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="228" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
         <v>716</v>
       </c>
@@ -15307,7 +15534,7 @@
         <v>9351425448</v>
       </c>
     </row>
-    <row r="229" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="229" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
         <v>716</v>
       </c>
@@ -15339,7 +15566,7 @@
         <v>8233813614</v>
       </c>
     </row>
-    <row r="230" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="230" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
         <v>716</v>
       </c>
@@ -15371,7 +15598,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="231" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="231" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
         <v>716</v>
       </c>
@@ -15403,7 +15630,7 @@
         <v>9351425448</v>
       </c>
     </row>
-    <row r="232" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="232" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
         <v>716</v>
       </c>
@@ -15435,7 +15662,7 @@
         <v>9351425448</v>
       </c>
     </row>
-    <row r="233" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="233" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
         <v>716</v>
       </c>
@@ -15467,7 +15694,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="234" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="234" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
         <v>716</v>
       </c>
@@ -15499,7 +15726,7 @@
         <v>9461617810</v>
       </c>
     </row>
-    <row r="235" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="235" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
         <v>716</v>
       </c>
@@ -15528,7 +15755,7 @@
         <v>8690260770</v>
       </c>
     </row>
-    <row r="236" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="236" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
         <v>716</v>
       </c>
@@ -15557,7 +15784,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="237" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="237" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
         <v>716</v>
       </c>
@@ -15586,7 +15813,7 @@
         <v>7737737743</v>
       </c>
     </row>
-    <row r="238" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="238" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
         <v>716</v>
       </c>
@@ -15615,7 +15842,7 @@
         <v>9929928611</v>
       </c>
     </row>
-    <row r="239" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="239" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>716</v>
       </c>
@@ -15644,7 +15871,7 @@
         <v>8952851012</v>
       </c>
     </row>
-    <row r="240" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="240" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
         <v>716</v>
       </c>
@@ -15673,7 +15900,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="241" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="241" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
         <v>716</v>
       </c>
@@ -15702,7 +15929,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="242" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="242" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
         <v>716</v>
       </c>
@@ -15731,7 +15958,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="243" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="243" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
         <v>716</v>
       </c>
@@ -15760,7 +15987,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="244" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="244" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
         <v>716</v>
       </c>
@@ -15789,7 +16016,7 @@
         <v>9584832221</v>
       </c>
     </row>
-    <row r="245" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="245" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
         <v>717</v>
       </c>
@@ -15818,7 +16045,7 @@
         <v>9414377779</v>
       </c>
     </row>
-    <row r="246" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="246" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
         <v>717</v>
       </c>
@@ -15847,7 +16074,7 @@
         <v>9414031265</v>
       </c>
     </row>
-    <row r="247" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="247" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
         <v>716</v>
       </c>
@@ -15876,7 +16103,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="248" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="248" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
         <v>716</v>
       </c>
@@ -15905,7 +16132,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="249" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="249" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
         <v>716</v>
       </c>
@@ -15934,7 +16161,7 @@
         <v>9414426145</v>
       </c>
     </row>
-    <row r="250" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="250" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B250" t="s">
         <v>716</v>
       </c>
@@ -15963,7 +16190,7 @@
         <v>6378452922</v>
       </c>
     </row>
-    <row r="251" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="251" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
         <v>716</v>
       </c>
@@ -15992,7 +16219,7 @@
         <v>9772201596</v>
       </c>
     </row>
-    <row r="252" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="252" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
         <v>716</v>
       </c>
@@ -16021,7 +16248,7 @@
         <v>7014129218</v>
       </c>
     </row>
-    <row r="253" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="253" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
         <v>716</v>
       </c>
@@ -16050,7 +16277,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="254" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="254" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G254" t="s">
         <v>752</v>
       </c>
@@ -16079,7 +16306,7 @@
         <v>8946947604</v>
       </c>
     </row>
-    <row r="255" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="255" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G255" t="s">
         <v>753</v>
       </c>
@@ -16108,7 +16335,7 @@
         <v>8094094709</v>
       </c>
     </row>
-    <row r="256" spans="2:15" x14ac:dyDescent="0.4">
+    <row r="256" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G256" t="s">
         <v>754</v>
       </c>
@@ -16137,7 +16364,7 @@
         <v>7688962275</v>
       </c>
     </row>
-    <row r="257" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="257" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G257" t="s">
         <v>755</v>
       </c>
@@ -16166,7 +16393,7 @@
         <v>7615841222</v>
       </c>
     </row>
-    <row r="258" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="258" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G258" t="s">
         <v>756</v>
       </c>
@@ -16195,7 +16422,7 @@
         <v>8946947604</v>
       </c>
     </row>
-    <row r="259" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="259" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G259" t="s">
         <v>757</v>
       </c>
@@ -16224,7 +16451,7 @@
         <v>8094094709</v>
       </c>
     </row>
-    <row r="260" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="260" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G260" t="s">
         <v>758</v>
       </c>
@@ -16253,7 +16480,7 @@
         <v>8114465301</v>
       </c>
     </row>
-    <row r="261" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="261" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G261" t="s">
         <v>759</v>
       </c>
@@ -16282,7 +16509,7 @@
         <v>7426972748</v>
       </c>
     </row>
-    <row r="262" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="262" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G262" t="s">
         <v>760</v>
       </c>
@@ -16311,7 +16538,7 @@
         <v>8946947604</v>
       </c>
     </row>
-    <row r="263" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="263" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G263" t="s">
         <v>761</v>
       </c>
@@ -16340,7 +16567,7 @@
         <v>7426972748</v>
       </c>
     </row>
-    <row r="264" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="264" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G264" t="s">
         <v>762</v>
       </c>
@@ -16369,7 +16596,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="265" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="265" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G265" t="s">
         <v>763</v>
       </c>
@@ -16398,7 +16625,7 @@
         <v>9413376468</v>
       </c>
     </row>
-    <row r="266" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="266" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G266" t="s">
         <v>764</v>
       </c>
@@ -16427,7 +16654,7 @@
         <v>8824950701</v>
       </c>
     </row>
-    <row r="267" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="267" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G267" t="s">
         <v>765</v>
       </c>
@@ -16453,7 +16680,7 @@
         <v>9928226750</v>
       </c>
     </row>
-    <row r="268" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="268" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G268" t="s">
         <v>766</v>
       </c>
@@ -16479,7 +16706,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="269" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="269" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G269" t="s">
         <v>767</v>
       </c>
@@ -16502,7 +16729,7 @@
         <v>9928226750</v>
       </c>
     </row>
-    <row r="270" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="270" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G270" t="s">
         <v>768</v>
       </c>
@@ -16531,7 +16758,7 @@
         <v>9785066887</v>
       </c>
     </row>
-    <row r="271" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="271" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G271" t="s">
         <v>769</v>
       </c>
@@ -16557,7 +16784,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="272" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="272" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G272" t="s">
         <v>770</v>
       </c>
@@ -16586,7 +16813,7 @@
         <v>7014528050</v>
       </c>
     </row>
-    <row r="273" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="273" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G273" t="s">
         <v>771</v>
       </c>
@@ -16615,7 +16842,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="274" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="274" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G274" t="s">
         <v>772</v>
       </c>
@@ -16644,7 +16871,7 @@
         <v>9530478275</v>
       </c>
     </row>
-    <row r="275" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="275" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G275" t="s">
         <v>773</v>
       </c>
@@ -16673,7 +16900,7 @@
         <v>8949181228</v>
       </c>
     </row>
-    <row r="276" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="276" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G276" t="s">
         <v>774</v>
       </c>
@@ -16702,7 +16929,7 @@
         <v>9887132638</v>
       </c>
     </row>
-    <row r="277" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="277" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G277" t="s">
         <v>775</v>
       </c>
@@ -16731,7 +16958,7 @@
         <v>6377562741</v>
       </c>
     </row>
-    <row r="278" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="278" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G278" t="s">
         <v>776</v>
       </c>
@@ -16760,7 +16987,7 @@
         <v>9982218415</v>
       </c>
     </row>
-    <row r="279" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="279" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G279" t="s">
         <v>777</v>
       </c>
@@ -16789,7 +17016,7 @@
         <v>7372990394</v>
       </c>
     </row>
-    <row r="280" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="280" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G280" t="s">
         <v>778</v>
       </c>
@@ -16818,7 +17045,7 @@
         <v>8302898240</v>
       </c>
     </row>
-    <row r="281" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="281" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G281" t="s">
         <v>779</v>
       </c>
@@ -16847,7 +17074,7 @@
         <v>6367586135</v>
       </c>
     </row>
-    <row r="282" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="282" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G282" t="s">
         <v>780</v>
       </c>
@@ -16876,7 +17103,7 @@
         <v>9571967602</v>
       </c>
     </row>
-    <row r="283" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="283" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G283" t="s">
         <v>781</v>
       </c>
@@ -16905,7 +17132,7 @@
         <v>9509169446</v>
       </c>
     </row>
-    <row r="284" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="284" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G284" t="s">
         <v>782</v>
       </c>
@@ -16934,7 +17161,7 @@
         <v>9660022000</v>
       </c>
     </row>
-    <row r="285" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="285" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G285" t="s">
         <v>783</v>
       </c>
@@ -16963,7 +17190,7 @@
         <v>9660022000</v>
       </c>
     </row>
-    <row r="286" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="286" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G286" t="s">
         <v>784</v>
       </c>
@@ -16992,7 +17219,7 @@
         <v>9660022000</v>
       </c>
     </row>
-    <row r="287" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="287" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G287" t="s">
         <v>785</v>
       </c>
@@ -17021,7 +17248,7 @@
         <v>960022000</v>
       </c>
     </row>
-    <row r="288" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="288" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G288" t="s">
         <v>786</v>
       </c>
@@ -17050,7 +17277,7 @@
         <v>9950695995</v>
       </c>
     </row>
-    <row r="289" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="289" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G289" t="s">
         <v>787</v>
       </c>
@@ -17079,7 +17306,7 @@
         <v>9873079066</v>
       </c>
     </row>
-    <row r="290" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="290" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G290" t="s">
         <v>788</v>
       </c>
@@ -17108,7 +17335,7 @@
         <v>9660022000</v>
       </c>
     </row>
-    <row r="291" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="291" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G291" t="s">
         <v>789</v>
       </c>
@@ -17137,7 +17364,7 @@
         <v>9660022000</v>
       </c>
     </row>
-    <row r="292" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="292" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G292" t="s">
         <v>790</v>
       </c>
@@ -17166,7 +17393,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="293" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="293" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G293" t="s">
         <v>791</v>
       </c>
@@ -17195,7 +17422,7 @@
         <v>9950660444</v>
       </c>
     </row>
-    <row r="294" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="294" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G294" t="s">
         <v>792</v>
       </c>
@@ -17224,7 +17451,7 @@
         <v>7014941458</v>
       </c>
     </row>
-    <row r="295" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="295" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G295" t="s">
         <v>793</v>
       </c>
@@ -17253,7 +17480,7 @@
         <v>9950660444</v>
       </c>
     </row>
-    <row r="296" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="296" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G296" t="s">
         <v>794</v>
       </c>
@@ -17282,7 +17509,7 @@
         <v>9667703107</v>
       </c>
     </row>
-    <row r="297" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="297" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G297" t="s">
         <v>795</v>
       </c>
@@ -17311,7 +17538,7 @@
         <v>9950660444</v>
       </c>
     </row>
-    <row r="298" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="298" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G298" t="s">
         <v>796</v>
       </c>
@@ -17340,7 +17567,7 @@
         <v>9950660444</v>
       </c>
     </row>
-    <row r="299" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="299" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G299" t="s">
         <v>797</v>
       </c>
@@ -17369,7 +17596,7 @@
         <v>8209748641</v>
       </c>
     </row>
-    <row r="300" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="300" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G300" t="s">
         <v>798</v>
       </c>
@@ -17395,7 +17622,7 @@
         <v>9667121144</v>
       </c>
     </row>
-    <row r="301" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="301" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G301" t="s">
         <v>799</v>
       </c>
@@ -17424,7 +17651,7 @@
         <v>9950660444</v>
       </c>
     </row>
-    <row r="302" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="302" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G302" t="s">
         <v>800</v>
       </c>
@@ -17453,7 +17680,7 @@
         <v>9667121144</v>
       </c>
     </row>
-    <row r="303" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="303" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G303" t="s">
         <v>801</v>
       </c>
@@ -17482,7 +17709,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="304" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="304" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G304" t="s">
         <v>802</v>
       </c>
@@ -17511,7 +17738,7 @@
         <v>9928499958</v>
       </c>
     </row>
-    <row r="305" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="305" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G305" t="s">
         <v>803</v>
       </c>
@@ -17540,7 +17767,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="306" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="306" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G306" t="s">
         <v>804</v>
       </c>
@@ -17569,7 +17796,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="307" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="307" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G307" t="s">
         <v>805</v>
       </c>
@@ -17598,7 +17825,7 @@
         <v>9828150030</v>
       </c>
     </row>
-    <row r="308" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="308" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G308" t="s">
         <v>806</v>
       </c>
@@ -17627,7 +17854,7 @@
         <v>9828150030</v>
       </c>
     </row>
-    <row r="309" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="309" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G309" t="s">
         <v>807</v>
       </c>
@@ -17656,7 +17883,7 @@
         <v>9828150030</v>
       </c>
     </row>
-    <row r="310" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="310" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G310" t="s">
         <v>808</v>
       </c>
@@ -17685,7 +17912,7 @@
         <v>9828150030</v>
       </c>
     </row>
-    <row r="311" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="311" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G311" t="s">
         <v>809</v>
       </c>
@@ -17714,7 +17941,7 @@
         <v>9828150030</v>
       </c>
     </row>
-    <row r="312" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="312" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G312" t="s">
         <v>810</v>
       </c>
@@ -17743,7 +17970,7 @@
         <v>9828150030</v>
       </c>
     </row>
-    <row r="313" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="313" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G313" t="s">
         <v>811</v>
       </c>
@@ -17772,7 +17999,7 @@
         <v>9928802510</v>
       </c>
     </row>
-    <row r="314" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="314" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G314" t="s">
         <v>812</v>
       </c>
@@ -17801,7 +18028,7 @@
         <v>9001716311</v>
       </c>
     </row>
-    <row r="315" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="315" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G315" t="s">
         <v>813</v>
       </c>
@@ -17830,7 +18057,7 @@
         <v>8440058069</v>
       </c>
     </row>
-    <row r="316" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="316" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G316" t="s">
         <v>814</v>
       </c>
@@ -17859,7 +18086,7 @@
         <v>8094072556</v>
       </c>
     </row>
-    <row r="317" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="317" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G317" t="s">
         <v>815</v>
       </c>
@@ -17888,7 +18115,7 @@
         <v>9414322722</v>
       </c>
     </row>
-    <row r="318" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="318" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G318" t="s">
         <v>816</v>
       </c>
@@ -17917,7 +18144,7 @@
         <v>9414322722</v>
       </c>
     </row>
-    <row r="319" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="319" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G319" t="s">
         <v>817</v>
       </c>
@@ -17946,7 +18173,7 @@
         <v>7733843870</v>
       </c>
     </row>
-    <row r="320" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="320" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G320" t="s">
         <v>818</v>
       </c>
@@ -17975,7 +18202,7 @@
         <v>9024141359</v>
       </c>
     </row>
-    <row r="321" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="321" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G321" t="s">
         <v>819</v>
       </c>
@@ -18004,7 +18231,7 @@
         <v>8058907986</v>
       </c>
     </row>
-    <row r="322" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="322" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G322" t="s">
         <v>820</v>
       </c>
@@ -18033,7 +18260,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="323" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="323" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G323" t="s">
         <v>821</v>
       </c>
@@ -18062,7 +18289,7 @@
         <v>9828060948</v>
       </c>
     </row>
-    <row r="324" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="324" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G324" t="s">
         <v>822</v>
       </c>
@@ -18091,7 +18318,7 @@
         <v>9829520133</v>
       </c>
     </row>
-    <row r="325" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="325" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G325" t="s">
         <v>823</v>
       </c>
@@ -18120,7 +18347,7 @@
         <v>9828060948</v>
       </c>
     </row>
-    <row r="326" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="326" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G326" t="s">
         <v>824</v>
       </c>
@@ -18149,7 +18376,7 @@
         <v>9829520133</v>
       </c>
     </row>
-    <row r="327" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="327" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G327" t="s">
         <v>825</v>
       </c>
@@ -18178,7 +18405,7 @@
         <v>9414042473</v>
       </c>
     </row>
-    <row r="328" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="328" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G328" t="s">
         <v>826</v>
       </c>
@@ -18207,7 +18434,7 @@
         <v>9928842000</v>
       </c>
     </row>
-    <row r="329" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="329" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G329" t="s">
         <v>827</v>
       </c>
@@ -18236,7 +18463,7 @@
         <v>9636767925</v>
       </c>
     </row>
-    <row r="330" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="330" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G330" t="s">
         <v>828</v>
       </c>
@@ -18262,7 +18489,7 @@
         <v>8290111372</v>
       </c>
     </row>
-    <row r="331" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="331" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G331" t="s">
         <v>829</v>
       </c>
@@ -18288,7 +18515,7 @@
         <v>8824946331</v>
       </c>
     </row>
-    <row r="332" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="332" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G332" t="s">
         <v>830</v>
       </c>
@@ -18314,7 +18541,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="333" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="333" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G333" t="s">
         <v>831</v>
       </c>
@@ -18340,7 +18567,7 @@
         <v>7891257050</v>
       </c>
     </row>
-    <row r="334" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="334" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G334" t="s">
         <v>832</v>
       </c>
@@ -18366,7 +18593,7 @@
         <v>9929118165</v>
       </c>
     </row>
-    <row r="335" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="335" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G335" t="s">
         <v>833</v>
       </c>
@@ -18392,7 +18619,7 @@
         <v>9261902212</v>
       </c>
     </row>
-    <row r="336" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="336" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G336" t="s">
         <v>834</v>
       </c>
@@ -18418,7 +18645,7 @@
         <v>9261902223</v>
       </c>
     </row>
-    <row r="337" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="337" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G337" t="s">
         <v>835</v>
       </c>
@@ -18444,7 +18671,7 @@
         <v>9261901846</v>
       </c>
     </row>
-    <row r="338" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="338" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G338" t="s">
         <v>836</v>
       </c>
@@ -18470,7 +18697,7 @@
         <v>7727835599</v>
       </c>
     </row>
-    <row r="339" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="339" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G339" t="s">
         <v>837</v>
       </c>
@@ -18496,7 +18723,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="340" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="340" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G340" t="s">
         <v>838</v>
       </c>
@@ -18522,7 +18749,7 @@
         <v>9660333095</v>
       </c>
     </row>
-    <row r="341" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="341" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G341" t="s">
         <v>839</v>
       </c>
@@ -18548,7 +18775,7 @@
         <v>9602866584</v>
       </c>
     </row>
-    <row r="342" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="342" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G342" t="s">
         <v>840</v>
       </c>
@@ -18574,7 +18801,7 @@
         <v>9602866584</v>
       </c>
     </row>
-    <row r="343" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="343" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G343" t="s">
         <v>841</v>
       </c>
@@ -18600,7 +18827,7 @@
         <v>8009536584</v>
       </c>
     </row>
-    <row r="344" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="344" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G344" t="s">
         <v>842</v>
       </c>
@@ -18626,7 +18853,7 @@
         <v>7976041554</v>
       </c>
     </row>
-    <row r="345" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="345" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G345" t="s">
         <v>843</v>
       </c>
@@ -18652,7 +18879,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="346" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="346" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G346" t="s">
         <v>844</v>
       </c>
@@ -18678,7 +18905,7 @@
         <v>9660333095</v>
       </c>
     </row>
-    <row r="347" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="347" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G347" t="s">
         <v>845</v>
       </c>
@@ -18704,7 +18931,7 @@
         <v>7976041554</v>
       </c>
     </row>
-    <row r="348" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="348" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G348" t="s">
         <v>846</v>
       </c>
@@ -18730,7 +18957,7 @@
         <v>7976041554</v>
       </c>
     </row>
-    <row r="349" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="349" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G349" t="s">
         <v>847</v>
       </c>
@@ -18756,7 +18983,7 @@
         <v>7014912174</v>
       </c>
     </row>
-    <row r="350" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="350" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G350" t="s">
         <v>489</v>
       </c>
@@ -18782,7 +19009,7 @@
         <v>9413288405</v>
       </c>
     </row>
-    <row r="351" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="351" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G351" t="s">
         <v>848</v>
       </c>
@@ -18808,7 +19035,7 @@
         <v>9001754998</v>
       </c>
     </row>
-    <row r="352" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="352" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G352" t="s">
         <v>849</v>
       </c>
@@ -18834,7 +19061,7 @@
         <v>9001754998</v>
       </c>
     </row>
-    <row r="353" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="353" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G353" t="s">
         <v>850</v>
       </c>
@@ -18860,7 +19087,7 @@
         <v>9001754998</v>
       </c>
     </row>
-    <row r="354" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="354" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G354" t="s">
         <v>851</v>
       </c>
@@ -18886,7 +19113,7 @@
         <v>9001754998</v>
       </c>
     </row>
-    <row r="355" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="355" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G355" t="s">
         <v>852</v>
       </c>
@@ -18912,7 +19139,7 @@
         <v>9001754998</v>
       </c>
     </row>
-    <row r="356" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="356" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G356" t="s">
         <v>853</v>
       </c>
@@ -18938,7 +19165,7 @@
         <v>9414035319</v>
       </c>
     </row>
-    <row r="357" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="357" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G357" t="s">
         <v>854</v>
       </c>
@@ -18964,7 +19191,7 @@
         <v>9660189881</v>
       </c>
     </row>
-    <row r="358" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="358" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G358" t="s">
         <v>855</v>
       </c>
@@ -18990,7 +19217,7 @@
         <v>9660189881</v>
       </c>
     </row>
-    <row r="359" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="359" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G359" t="s">
         <v>856</v>
       </c>
@@ -19016,7 +19243,7 @@
         <v>9660189881</v>
       </c>
     </row>
-    <row r="360" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="360" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G360" t="s">
         <v>857</v>
       </c>
@@ -19042,7 +19269,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="361" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="361" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G361" t="s">
         <v>858</v>
       </c>
@@ -19068,7 +19295,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="362" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="362" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G362" t="s">
         <v>859</v>
       </c>
@@ -19094,7 +19321,7 @@
         <v>8505003040</v>
       </c>
     </row>
-    <row r="363" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="363" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G363" t="s">
         <v>860</v>
       </c>
@@ -19120,7 +19347,7 @@
         <v>9549501238</v>
       </c>
     </row>
-    <row r="364" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="364" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G364" t="s">
         <v>861</v>
       </c>
@@ -19146,7 +19373,7 @@
         <v>9351507796</v>
       </c>
     </row>
-    <row r="365" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="365" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G365" t="s">
         <v>862</v>
       </c>
@@ -19172,7 +19399,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="366" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="366" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G366" t="s">
         <v>863</v>
       </c>
@@ -19198,7 +19425,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="367" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="367" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G367" t="s">
         <v>864</v>
       </c>
@@ -19224,7 +19451,7 @@
         <v>9828140082</v>
       </c>
     </row>
-    <row r="368" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="368" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G368" t="s">
         <v>865</v>
       </c>
@@ -19250,7 +19477,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="369" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="369" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G369" t="s">
         <v>866</v>
       </c>
@@ -19276,7 +19503,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="370" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="370" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G370" t="s">
         <v>867</v>
       </c>
@@ -19302,7 +19529,7 @@
         <v>9829095152</v>
       </c>
     </row>
-    <row r="371" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="371" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G371" t="s">
         <v>868</v>
       </c>
@@ -19328,7 +19555,7 @@
         <v>8003699013</v>
       </c>
     </row>
-    <row r="372" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="372" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G372" t="s">
         <v>869</v>
       </c>
@@ -19354,7 +19581,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="373" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="373" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G373" t="s">
         <v>870</v>
       </c>
@@ -19380,7 +19607,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="374" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="374" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G374" t="s">
         <v>871</v>
       </c>
@@ -19406,7 +19633,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="375" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="375" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G375" t="s">
         <v>872</v>
       </c>
@@ -19432,7 +19659,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="376" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="376" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G376" t="s">
         <v>873</v>
       </c>
@@ -19458,7 +19685,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="377" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="377" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G377" t="s">
         <v>874</v>
       </c>
@@ -19484,7 +19711,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="378" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="378" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G378" t="s">
         <v>875</v>
       </c>
@@ -19510,7 +19737,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="379" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="379" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G379" t="s">
         <v>876</v>
       </c>
@@ -19536,7 +19763,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="380" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="380" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G380" t="s">
         <v>877</v>
       </c>
@@ -19562,7 +19789,7 @@
         <v>9413489581</v>
       </c>
     </row>
-    <row r="381" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="381" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G381" t="s">
         <v>878</v>
       </c>
@@ -19588,7 +19815,7 @@
         <v>7733099751</v>
       </c>
     </row>
-    <row r="382" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="382" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G382" t="s">
         <v>879</v>
       </c>
@@ -19614,7 +19841,7 @@
         <v>9785279499</v>
       </c>
     </row>
-    <row r="383" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="383" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G383" t="s">
         <v>880</v>
       </c>
@@ -19640,7 +19867,7 @@
         <v>9785279499</v>
       </c>
     </row>
-    <row r="384" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="384" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G384" t="s">
         <v>881</v>
       </c>
@@ -19666,7 +19893,7 @@
         <v>9414614984</v>
       </c>
     </row>
-    <row r="385" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="385" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G385" t="s">
         <v>882</v>
       </c>
@@ -19692,7 +19919,7 @@
         <v>9785279499</v>
       </c>
     </row>
-    <row r="386" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="386" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G386" t="s">
         <v>883</v>
       </c>
@@ -19718,7 +19945,7 @@
         <v>9001199752</v>
       </c>
     </row>
-    <row r="387" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="387" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G387" t="s">
         <v>884</v>
       </c>
@@ -19744,7 +19971,7 @@
         <v>8450917737</v>
       </c>
     </row>
-    <row r="388" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="388" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G388" t="s">
         <v>885</v>
       </c>
@@ -19770,7 +19997,7 @@
         <v>9116636274</v>
       </c>
     </row>
-    <row r="389" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="389" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G389" t="s">
         <v>886</v>
       </c>
@@ -19796,7 +20023,7 @@
         <v>7014507181</v>
       </c>
     </row>
-    <row r="390" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="390" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G390" t="s">
         <v>887</v>
       </c>
@@ -19822,7 +20049,7 @@
         <v>9001199700</v>
       </c>
     </row>
-    <row r="391" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="391" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G391" t="s">
         <v>888</v>
       </c>
@@ -19848,7 +20075,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="392" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="392" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G392" t="s">
         <v>889</v>
       </c>
@@ -19874,7 +20101,7 @@
         <v>7793822536</v>
       </c>
     </row>
-    <row r="393" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="393" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G393" t="s">
         <v>890</v>
       </c>
@@ -19900,7 +20127,7 @@
         <v>9261900817</v>
       </c>
     </row>
-    <row r="394" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="394" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G394" t="s">
         <v>891</v>
       </c>
@@ -19926,7 +20153,7 @@
         <v>9636237665</v>
       </c>
     </row>
-    <row r="395" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="395" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G395" t="s">
         <v>892</v>
       </c>
@@ -19952,7 +20179,7 @@
         <v>9001939000</v>
       </c>
     </row>
-    <row r="396" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="396" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G396" t="s">
         <v>893</v>
       </c>
@@ -19978,7 +20205,7 @@
         <v>9530448443</v>
       </c>
     </row>
-    <row r="397" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="397" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G397" t="s">
         <v>894</v>
       </c>
@@ -20004,7 +20231,7 @@
         <v>9351229417</v>
       </c>
     </row>
-    <row r="398" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="398" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G398" t="s">
         <v>895</v>
       </c>
@@ -20030,7 +20257,7 @@
         <v>787783704</v>
       </c>
     </row>
-    <row r="399" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="399" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G399" t="s">
         <v>896</v>
       </c>
@@ -20056,7 +20283,7 @@
         <v>9928416693</v>
       </c>
     </row>
-    <row r="400" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="400" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G400" t="s">
         <v>897</v>
       </c>
@@ -20082,7 +20309,7 @@
         <v>8302030916</v>
       </c>
     </row>
-    <row r="401" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="401" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G401" t="s">
         <v>898</v>
       </c>
@@ -20108,7 +20335,7 @@
         <v>9414614984</v>
       </c>
     </row>
-    <row r="402" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="402" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G402" t="s">
         <v>899</v>
       </c>
@@ -20134,7 +20361,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="403" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="403" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G403" t="s">
         <v>900</v>
       </c>
@@ -20160,7 +20387,7 @@
         <v>8448895279</v>
       </c>
     </row>
-    <row r="404" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="404" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G404" t="s">
         <v>901</v>
       </c>
@@ -20186,7 +20413,7 @@
         <v>9887802666</v>
       </c>
     </row>
-    <row r="405" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="405" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G405" t="s">
         <v>902</v>
       </c>
@@ -20212,7 +20439,7 @@
         <v>8949577828</v>
       </c>
     </row>
-    <row r="406" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="406" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G406" t="s">
         <v>903</v>
       </c>
@@ -20238,7 +20465,7 @@
         <v>9001195668</v>
       </c>
     </row>
-    <row r="407" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="407" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G407" t="s">
         <v>904</v>
       </c>
@@ -20264,7 +20491,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="408" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="408" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G408" t="s">
         <v>905</v>
       </c>
@@ -20290,7 +20517,7 @@
         <v>9462137700</v>
       </c>
     </row>
-    <row r="409" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="409" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G409" t="s">
         <v>906</v>
       </c>
@@ -20316,7 +20543,7 @@
         <v>8619661880</v>
       </c>
     </row>
-    <row r="410" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="410" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G410" t="s">
         <v>907</v>
       </c>
@@ -20342,7 +20569,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="411" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="411" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G411" t="s">
         <v>908</v>
       </c>
@@ -20368,7 +20595,7 @@
         <v>9829193377</v>
       </c>
     </row>
-    <row r="412" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="412" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G412" t="s">
         <v>909</v>
       </c>
@@ -20394,7 +20621,7 @@
         <v>9694678222</v>
       </c>
     </row>
-    <row r="413" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="413" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G413" t="s">
         <v>910</v>
       </c>
@@ -20420,7 +20647,7 @@
         <v>7976417072</v>
       </c>
     </row>
-    <row r="414" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="414" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G414" t="s">
         <v>911</v>
       </c>
@@ -20446,7 +20673,7 @@
         <v>9001199281</v>
       </c>
     </row>
-    <row r="415" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="415" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G415" t="s">
         <v>912</v>
       </c>
@@ -20472,7 +20699,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="416" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="416" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G416" t="s">
         <v>913</v>
       </c>
@@ -20498,7 +20725,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="417" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="417" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G417" t="s">
         <v>914</v>
       </c>
@@ -20524,7 +20751,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="418" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="418" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G418" t="s">
         <v>915</v>
       </c>
@@ -20550,7 +20777,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="419" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="419" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G419" t="s">
         <v>916</v>
       </c>
@@ -20576,7 +20803,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="420" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="420" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G420" t="s">
         <v>917</v>
       </c>
@@ -20602,7 +20829,7 @@
         <v>6350203549</v>
       </c>
     </row>
-    <row r="421" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="421" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G421" t="s">
         <v>918</v>
       </c>
@@ -20628,7 +20855,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="422" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="422" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G422" t="s">
         <v>919</v>
       </c>
@@ -20654,7 +20881,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="423" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="423" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G423" t="s">
         <v>920</v>
       </c>
@@ -20680,7 +20907,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="424" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="424" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G424" t="s">
         <v>921</v>
       </c>
@@ -20706,7 +20933,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="425" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="425" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G425" t="s">
         <v>922</v>
       </c>
@@ -20732,7 +20959,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="426" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="426" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G426" t="s">
         <v>923</v>
       </c>
@@ -20758,7 +20985,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="427" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="427" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G427" t="s">
         <v>924</v>
       </c>
@@ -20784,7 +21011,7 @@
         <v>9001199207</v>
       </c>
     </row>
-    <row r="428" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="428" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G428" t="s">
         <v>925</v>
       </c>
@@ -20810,7 +21037,7 @@
         <v>9001199000</v>
       </c>
     </row>
-    <row r="429" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="429" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G429" t="s">
         <v>926</v>
       </c>
@@ -20836,7 +21063,7 @@
         <v>9330007700</v>
       </c>
     </row>
-    <row r="430" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="430" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G430" t="s">
         <v>927</v>
       </c>
@@ -20865,7 +21092,7 @@
         <v>8559932752</v>
       </c>
     </row>
-    <row r="431" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="431" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G431" t="s">
         <v>928</v>
       </c>
@@ -20894,7 +21121,7 @@
         <v>9928524788</v>
       </c>
     </row>
-    <row r="432" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="432" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G432" t="s">
         <v>929</v>
       </c>
@@ -20923,7 +21150,7 @@
         <v>8949611945</v>
       </c>
     </row>
-    <row r="433" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="433" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G433" t="s">
         <v>930</v>
       </c>
@@ -20952,7 +21179,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="434" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="434" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G434" t="s">
         <v>931</v>
       </c>
@@ -20981,7 +21208,7 @@
         <v>8058110241</v>
       </c>
     </row>
-    <row r="435" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="435" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G435" t="s">
         <v>932</v>
       </c>
@@ -21010,7 +21237,7 @@
         <v>9783461288</v>
       </c>
     </row>
-    <row r="436" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="436" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G436" t="s">
         <v>933</v>
       </c>
@@ -21039,7 +21266,7 @@
         <v>9414123468</v>
       </c>
     </row>
-    <row r="437" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="437" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G437" t="s">
         <v>934</v>
       </c>
@@ -21068,7 +21295,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="438" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="438" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G438" t="s">
         <v>935</v>
       </c>
@@ -21097,7 +21324,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="439" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="439" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G439" t="s">
         <v>936</v>
       </c>
@@ -21126,7 +21353,7 @@
         <v>8504093578</v>
       </c>
     </row>
-    <row r="440" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="440" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G440" t="s">
         <v>937</v>
       </c>
@@ -21155,7 +21382,7 @@
         <v>7838500968</v>
       </c>
     </row>
-    <row r="441" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="441" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G441" t="s">
         <v>938</v>
       </c>
@@ -21184,7 +21411,7 @@
         <v>8696969608</v>
       </c>
     </row>
-    <row r="442" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="442" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G442" t="s">
         <v>939</v>
       </c>
@@ -21213,7 +21440,7 @@
         <v>9414075223</v>
       </c>
     </row>
-    <row r="443" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="443" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G443" t="s">
         <v>940</v>
       </c>
@@ -21242,7 +21469,7 @@
         <v>9829313601</v>
       </c>
     </row>
-    <row r="444" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="444" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G444" t="s">
         <v>941</v>
       </c>
@@ -21271,7 +21498,7 @@
         <v>9251146007</v>
       </c>
     </row>
-    <row r="445" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="445" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G445" t="s">
         <v>942</v>
       </c>
@@ -21300,7 +21527,7 @@
         <v>9414032623</v>
       </c>
     </row>
-    <row r="446" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="446" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G446" t="s">
         <v>943</v>
       </c>
@@ -21329,7 +21556,7 @@
         <v>9910153007</v>
       </c>
     </row>
-    <row r="447" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="447" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G447" t="s">
         <v>944</v>
       </c>
@@ -21358,7 +21585,7 @@
         <v>8619762993</v>
       </c>
     </row>
-    <row r="448" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="448" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G448" t="s">
         <v>945</v>
       </c>
@@ -21387,7 +21614,7 @@
         <v>8861282015</v>
       </c>
     </row>
-    <row r="449" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="449" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G449" t="s">
         <v>946</v>
       </c>
@@ -21416,7 +21643,7 @@
         <v>8740895928</v>
       </c>
     </row>
-    <row r="450" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="450" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G450" t="s">
         <v>947</v>
       </c>
@@ -21445,7 +21672,7 @@
         <v>8740895928</v>
       </c>
     </row>
-    <row r="451" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="451" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G451" t="s">
         <v>948</v>
       </c>
@@ -21474,7 +21701,7 @@
         <v>8861282015</v>
       </c>
     </row>
-    <row r="452" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="452" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G452" t="s">
         <v>949</v>
       </c>
@@ -21503,7 +21730,7 @@
         <v>9829036902</v>
       </c>
     </row>
-    <row r="453" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="453" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G453" t="s">
         <v>950</v>
       </c>
@@ -21532,7 +21759,7 @@
         <v>9928106695</v>
       </c>
     </row>
-    <row r="454" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="454" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G454" t="s">
         <v>951</v>
       </c>
@@ -21561,7 +21788,7 @@
         <v>7023004000</v>
       </c>
     </row>
-    <row r="455" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="455" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G455" t="s">
         <v>952</v>
       </c>
@@ -21590,7 +21817,7 @@
         <v>9001195559</v>
       </c>
     </row>
-    <row r="456" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="456" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G456" t="s">
         <v>812</v>
       </c>
@@ -21619,7 +21846,7 @@
         <v>9910148625</v>
       </c>
     </row>
-    <row r="457" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="457" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G457" t="s">
         <v>953</v>
       </c>
@@ -21648,7 +21875,7 @@
         <v>9413432844</v>
       </c>
     </row>
-    <row r="458" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="458" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G458" t="s">
         <v>954</v>
       </c>
@@ -21677,7 +21904,7 @@
         <v>9782794341</v>
       </c>
     </row>
-    <row r="459" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="459" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G459" t="s">
         <v>955</v>
       </c>
@@ -21706,7 +21933,7 @@
         <v>9650950968</v>
       </c>
     </row>
-    <row r="460" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="460" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G460" t="s">
         <v>956</v>
       </c>
@@ -21735,7 +21962,7 @@
         <v>9829055956</v>
       </c>
     </row>
-    <row r="461" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="461" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G461" t="s">
         <v>957</v>
       </c>
@@ -21764,7 +21991,7 @@
         <v>9828087828</v>
       </c>
     </row>
-    <row r="462" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="462" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G462" t="s">
         <v>958</v>
       </c>
@@ -21793,7 +22020,7 @@
         <v>9887628112</v>
       </c>
     </row>
-    <row r="463" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="463" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G463" t="s">
         <v>959</v>
       </c>
@@ -21822,7 +22049,7 @@
         <v>9887153949</v>
       </c>
     </row>
-    <row r="464" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="464" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G464" t="s">
         <v>960</v>
       </c>
@@ -21851,7 +22078,7 @@
         <v>9414020201</v>
       </c>
     </row>
-    <row r="465" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="465" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G465" t="s">
         <v>961</v>
       </c>
@@ -21880,7 +22107,7 @@
         <v>7976594660</v>
       </c>
     </row>
-    <row r="466" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="466" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G466" t="s">
         <v>962</v>
       </c>
@@ -21909,7 +22136,7 @@
         <v>9413906890</v>
       </c>
     </row>
-    <row r="467" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="467" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G467" t="s">
         <v>963</v>
       </c>
@@ -21938,7 +22165,7 @@
         <v>9414326514</v>
       </c>
     </row>
-    <row r="468" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="468" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G468" t="s">
         <v>964</v>
       </c>
@@ -21967,7 +22194,7 @@
         <v>9983577711</v>
       </c>
     </row>
-    <row r="469" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="469" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G469" t="s">
         <v>965</v>
       </c>
@@ -21996,7 +22223,7 @@
         <v>9829063962</v>
       </c>
     </row>
-    <row r="470" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="470" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G470" t="s">
         <v>966</v>
       </c>
@@ -22025,7 +22252,7 @@
         <v>9829053122</v>
       </c>
     </row>
-    <row r="471" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="471" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G471" t="s">
         <v>967</v>
       </c>
@@ -22054,7 +22281,7 @@
         <v>7042960810</v>
       </c>
     </row>
-    <row r="472" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="472" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G472" t="s">
         <v>968</v>
       </c>
@@ -22083,7 +22310,7 @@
         <v>9829374567</v>
       </c>
     </row>
-    <row r="473" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="473" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G473" t="s">
         <v>969</v>
       </c>
@@ -22112,7 +22339,7 @@
         <v>9929377766</v>
       </c>
     </row>
-    <row r="474" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="474" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G474" t="s">
         <v>970</v>
       </c>
@@ -22141,7 +22368,7 @@
         <v>9530400116</v>
       </c>
     </row>
-    <row r="475" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="475" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G475" t="s">
         <v>971</v>
       </c>
@@ -22170,7 +22397,7 @@
         <v>9468891113</v>
       </c>
     </row>
-    <row r="476" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="476" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G476" t="s">
         <v>972</v>
       </c>
@@ -22199,7 +22426,7 @@
         <v>9001993656</v>
       </c>
     </row>
-    <row r="477" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="477" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G477" t="s">
         <v>973</v>
       </c>
@@ -22228,7 +22455,7 @@
         <v>9829133050</v>
       </c>
     </row>
-    <row r="478" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="478" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G478" t="s">
         <v>974</v>
       </c>
@@ -22257,7 +22484,7 @@
         <v>9772157693</v>
       </c>
     </row>
-    <row r="479" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="479" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G479" t="s">
         <v>975</v>
       </c>
@@ -22286,7 +22513,7 @@
         <v>9351922618</v>
       </c>
     </row>
-    <row r="480" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="480" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G480" t="s">
         <v>976</v>
       </c>
@@ -22315,7 +22542,7 @@
         <v>8290300000</v>
       </c>
     </row>
-    <row r="481" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="481" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G481" t="s">
         <v>977</v>
       </c>
@@ -22344,7 +22571,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="482" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="482" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G482" t="s">
         <v>978</v>
       </c>
@@ -22373,7 +22600,7 @@
         <v>9470308024</v>
       </c>
     </row>
-    <row r="483" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="483" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G483" t="s">
         <v>979</v>
       </c>
@@ -22402,7 +22629,7 @@
         <v>9829861505</v>
       </c>
     </row>
-    <row r="484" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="484" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G484" t="s">
         <v>980</v>
       </c>
@@ -22431,7 +22658,7 @@
         <v>9829103956</v>
       </c>
     </row>
-    <row r="485" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="485" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G485" t="s">
         <v>981</v>
       </c>
@@ -22460,7 +22687,7 @@
         <v>9470308024</v>
       </c>
     </row>
-    <row r="486" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="486" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G486" t="s">
         <v>982</v>
       </c>
@@ -22489,7 +22716,7 @@
         <v>9470308024</v>
       </c>
     </row>
-    <row r="487" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="487" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G487" t="s">
         <v>983</v>
       </c>
@@ -22518,7 +22745,7 @@
         <v>8952000025</v>
       </c>
     </row>
-    <row r="488" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="488" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G488" t="s">
         <v>984</v>
       </c>
@@ -22547,7 +22774,7 @@
         <v>9079130946</v>
       </c>
     </row>
-    <row r="489" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="489" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G489" t="s">
         <v>985</v>
       </c>
@@ -22576,7 +22803,7 @@
         <v>9829052022</v>
       </c>
     </row>
-    <row r="490" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="490" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G490" t="s">
         <v>986</v>
       </c>
@@ -22605,7 +22832,7 @@
         <v>9667321921</v>
       </c>
     </row>
-    <row r="491" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="491" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G491" t="s">
         <v>987</v>
       </c>
@@ -22634,7 +22861,7 @@
         <v>7597058523</v>
       </c>
     </row>
-    <row r="492" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="492" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G492" t="s">
         <v>988</v>
       </c>
@@ -22663,7 +22890,7 @@
         <v>9694423240</v>
       </c>
     </row>
-    <row r="493" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="493" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G493" t="s">
         <v>989</v>
       </c>
@@ -22692,7 +22919,7 @@
         <v>9680096530</v>
       </c>
     </row>
-    <row r="494" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="494" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G494" t="s">
         <v>990</v>
       </c>
@@ -22721,7 +22948,7 @@
         <v>8440979283</v>
       </c>
     </row>
-    <row r="495" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="495" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G495" t="s">
         <v>991</v>
       </c>
@@ -22750,7 +22977,7 @@
         <v>9829246123</v>
       </c>
     </row>
-    <row r="496" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="496" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G496" t="s">
         <v>992</v>
       </c>
@@ -22779,7 +23006,7 @@
         <v>9829246123</v>
       </c>
     </row>
-    <row r="497" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="497" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G497" t="s">
         <v>993</v>
       </c>
@@ -22808,7 +23035,7 @@
         <v>9829277763</v>
       </c>
     </row>
-    <row r="498" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="498" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G498" t="s">
         <v>760</v>
       </c>
@@ -22837,7 +23064,7 @@
         <v>8890198066</v>
       </c>
     </row>
-    <row r="499" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="499" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G499" t="s">
         <v>994</v>
       </c>
@@ -22866,7 +23093,7 @@
         <v>9799064833</v>
       </c>
     </row>
-    <row r="500" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="500" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G500" t="s">
         <v>995</v>
       </c>
@@ -22895,7 +23122,7 @@
         <v>9672044446</v>
       </c>
     </row>
-    <row r="501" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="501" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G501" t="s">
         <v>996</v>
       </c>
@@ -22924,7 +23151,7 @@
         <v>9887799717</v>
       </c>
     </row>
-    <row r="502" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="502" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G502" t="s">
         <v>997</v>
       </c>
@@ -22953,7 +23180,7 @@
         <v>9828959799</v>
       </c>
     </row>
-    <row r="503" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="503" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G503" t="s">
         <v>998</v>
       </c>
@@ -22982,7 +23209,7 @@
         <v>9168485614</v>
       </c>
     </row>
-    <row r="504" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="504" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G504" t="s">
         <v>999</v>
       </c>
@@ -23011,7 +23238,7 @@
         <v>9422572292</v>
       </c>
     </row>
-    <row r="505" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="505" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G505" t="s">
         <v>1000</v>
       </c>
@@ -23040,7 +23267,7 @@
         <v>9887683489</v>
       </c>
     </row>
-    <row r="506" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="506" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G506" t="s">
         <v>1001</v>
       </c>
@@ -23069,7 +23296,7 @@
         <v>8826103072</v>
       </c>
     </row>
-    <row r="507" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="507" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G507" t="s">
         <v>1002</v>
       </c>
@@ -23098,7 +23325,7 @@
         <v>9828302373</v>
       </c>
     </row>
-    <row r="508" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="508" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G508" t="s">
         <v>1003</v>
       </c>
@@ -23127,7 +23354,7 @@
         <v>9713347635</v>
       </c>
     </row>
-    <row r="509" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="509" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G509" t="s">
         <v>1004</v>
       </c>
@@ -23156,7 +23383,7 @@
         <v>9785246797</v>
       </c>
     </row>
-    <row r="510" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="510" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G510" t="s">
         <v>1005</v>
       </c>
@@ -23185,7 +23412,7 @@
         <v>9414405416</v>
       </c>
     </row>
-    <row r="511" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="511" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G511" t="s">
         <v>1006</v>
       </c>
@@ -23214,7 +23441,7 @@
         <v>9812075333</v>
       </c>
     </row>
-    <row r="512" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="512" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G512" t="s">
         <v>1007</v>
       </c>
@@ -23243,7 +23470,7 @@
         <v>9928827248</v>
       </c>
     </row>
-    <row r="513" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="513" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G513" t="s">
         <v>1008</v>
       </c>
@@ -23272,7 +23499,7 @@
         <v>8441886287</v>
       </c>
     </row>
-    <row r="514" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="514" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G514" t="s">
         <v>1009</v>
       </c>
@@ -23301,7 +23528,7 @@
         <v>9314011123</v>
       </c>
     </row>
-    <row r="515" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="515" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G515" t="s">
         <v>1010</v>
       </c>
@@ -23330,7 +23557,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="516" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="516" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G516" t="s">
         <v>1011</v>
       </c>
@@ -23359,7 +23586,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="517" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="517" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G517" t="s">
         <v>1012</v>
       </c>
@@ -23388,7 +23615,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="518" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="518" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G518" t="s">
         <v>1013</v>
       </c>
@@ -23417,7 +23644,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="519" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="519" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G519" t="s">
         <v>1014</v>
       </c>
@@ -23446,7 +23673,7 @@
         <v>9887797804</v>
       </c>
     </row>
-    <row r="520" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="520" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G520" t="s">
         <v>1015</v>
       </c>
@@ -23475,7 +23702,7 @@
         <v>9571828262</v>
       </c>
     </row>
-    <row r="521" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="521" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G521" t="s">
         <v>1016</v>
       </c>
@@ -23504,7 +23731,7 @@
         <v>8890148674</v>
       </c>
     </row>
-    <row r="522" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="522" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G522" t="s">
         <v>1017</v>
       </c>
@@ -23533,7 +23760,7 @@
         <v>9929353395</v>
       </c>
     </row>
-    <row r="523" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="523" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G523" t="s">
         <v>1018</v>
       </c>
@@ -23562,7 +23789,7 @@
         <v>8003951513</v>
       </c>
     </row>
-    <row r="524" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="524" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G524" t="s">
         <v>1019</v>
       </c>
@@ -23591,7 +23818,7 @@
         <v>8003951513</v>
       </c>
     </row>
-    <row r="525" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="525" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G525" t="s">
         <v>1020</v>
       </c>
@@ -23620,7 +23847,7 @@
         <v>8302827787</v>
       </c>
     </row>
-    <row r="526" spans="7:15" x14ac:dyDescent="0.4">
+    <row r="526" spans="3:18" x14ac:dyDescent="0.25">
       <c r="G526" t="s">
         <v>1021</v>
       </c>
@@ -23649,47 +23876,3218 @@
         <v>8058879682</v>
       </c>
     </row>
+    <row r="527" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C527" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="G527" s="6" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H527" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J527" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K527" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L527" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M527" s="4">
+        <v>8788840080</v>
+      </c>
+      <c r="N527" s="11" t="s">
+        <v>1346</v>
+      </c>
+      <c r="R527" s="3">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="528" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C528" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G528" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="H528" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J528" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K528" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L528" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M528" s="4">
+        <v>9555963399</v>
+      </c>
+      <c r="N528" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="R528" s="3">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="529" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C529" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="G529" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="H529" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J529" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K529" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L529" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M529" s="4">
+        <v>9887666006</v>
+      </c>
+      <c r="N529" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="R529" s="3">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="530" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C530" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="G530" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="H530" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J530" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K530" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L530" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M530" s="4">
+        <v>9461366141</v>
+      </c>
+      <c r="N530" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="R530" s="3">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="531" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C531" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G531" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="H531" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J531" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K531" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L531" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M531" s="4">
+        <v>9460974100</v>
+      </c>
+      <c r="N531" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="R531" s="3">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="532" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C532" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="G532" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="H532" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J532" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K532" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L532" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M532" s="4">
+        <v>9413449700</v>
+      </c>
+      <c r="N532" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="R532" s="3">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="533" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C533" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="G533" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="H533" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J533" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K533" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L533" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M533" s="4">
+        <v>8107144304</v>
+      </c>
+      <c r="N533" s="11" t="s">
+        <v>605</v>
+      </c>
+      <c r="R533" s="3">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="534" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C534" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="G534" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="H534" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J534" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K534" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L534" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M534" s="4">
+        <v>8955672959</v>
+      </c>
+      <c r="N534" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="R534" s="3">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="535" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C535" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="G535" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="H535" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J535" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K535" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L535" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M535" s="4">
+        <v>8852833381</v>
+      </c>
+      <c r="N535" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="R535" s="3">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="536" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C536" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="G536" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="H536" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J536" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K536" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L536" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M536" s="4">
+        <v>9660635309</v>
+      </c>
+      <c r="N536" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="R536" s="3">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="537" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C537" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="G537" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="H537" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J537" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K537" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L537" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M537" s="4">
+        <v>9340312869</v>
+      </c>
+      <c r="N537" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="R537" s="3">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="538" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C538" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="G538" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="H538" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J538" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K538" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L538" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M538" s="4">
+        <v>9587889799</v>
+      </c>
+      <c r="N538" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="R538" s="3">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="539" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C539" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="G539" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="H539" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J539" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K539" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L539" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M539" s="4">
+        <v>9928018257</v>
+      </c>
+      <c r="N539" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="R539" s="3">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="540" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C540" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G540" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="H540" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J540" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K540" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L540" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M540" s="4">
+        <v>9799173300</v>
+      </c>
+      <c r="N540" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="R540" s="3">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="541" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C541" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G541" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="H541" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J541" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K541" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L541" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M541" s="4">
+        <v>9636884077</v>
+      </c>
+      <c r="N541" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="R541" s="3">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="542" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C542" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="G542" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="H542" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J542" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="K542" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L542" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M542" s="4">
+        <v>7976209105</v>
+      </c>
+      <c r="N542" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="R542" s="3">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="543" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C543" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G543" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="H543" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J543" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K543" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L543" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M543" s="4">
+        <v>9757216007</v>
+      </c>
+      <c r="N543" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="R543" s="3">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="544" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C544" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G544" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="H544" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J544" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K544" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L544" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M544" s="4">
+        <v>8303009716</v>
+      </c>
+      <c r="N544" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="R544" s="3">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="545" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C545" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="G545" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="H545" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J545" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K545" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L545" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M545" s="4">
+        <v>8432165488</v>
+      </c>
+      <c r="N545" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="R545" s="3">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="546" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C546" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G546" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="H546" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J546" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K546" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L546" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M546" s="4">
+        <v>9829942150</v>
+      </c>
+      <c r="N546" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="R546" s="3">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="547" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C547" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="G547" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="H547" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J547" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K547" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L547" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M547" s="4">
+        <v>9950378418</v>
+      </c>
+      <c r="N547" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="R547" s="3">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="548" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C548" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="G548" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="H548" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J548" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K548" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L548" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M548" s="4">
+        <v>8764009796</v>
+      </c>
+      <c r="N548" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="R548" s="3">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="549" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C549" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="G549" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="H549" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J549" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K549" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L549" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M549" s="4">
+        <v>9799885744</v>
+      </c>
+      <c r="N549" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="R549" s="3">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="550" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C550" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="G550" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="H550" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J550" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K550" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L550" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M550" s="4">
+        <v>8587879534</v>
+      </c>
+      <c r="N550" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="R550" s="3">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="551" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C551" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="G551" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="H551" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J551" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="K551" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L551" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M551" s="4">
+        <v>9166943045</v>
+      </c>
+      <c r="N551" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="R551" s="3">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="552" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C552" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="G552" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="H552" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J552" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K552" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L552" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M552" s="4">
+        <v>7877485050</v>
+      </c>
+      <c r="N552" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="R552" s="3">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="553" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C553" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G553" s="6" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H553" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J553" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K553" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L553" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M553" s="4">
+        <v>8384939365</v>
+      </c>
+      <c r="N553" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="R553" s="3">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="554" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C554" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G554" s="6" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H554" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J554" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K554" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L554" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M554" s="4">
+        <v>9470586950</v>
+      </c>
+      <c r="N554" s="11" t="s">
+        <v>1252</v>
+      </c>
+      <c r="R554" s="3">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="555" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C555" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G555" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="H555" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J555" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K555" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L555" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M555" s="4">
+        <v>9799173300</v>
+      </c>
+      <c r="N555" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="R555" s="3">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="556" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C556" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G556" s="6" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H556" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J556" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K556" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L556" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M556" s="4">
+        <v>9887110033</v>
+      </c>
+      <c r="N556" s="11" t="s">
+        <v>1347</v>
+      </c>
+      <c r="R556" s="3">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="557" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C557" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G557" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H557" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J557" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K557" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L557" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M557" s="4">
+        <v>9782893333</v>
+      </c>
+      <c r="N557" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="R557" s="3">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="558" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C558" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G558" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H558" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J558" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K558" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L558" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M558" s="4">
+        <v>6375224741</v>
+      </c>
+      <c r="N558" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="R558" s="3">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="559" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C559" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G559" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H559" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J559" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K559" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L559" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M559" s="4">
+        <v>8626993152</v>
+      </c>
+      <c r="N559" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="R559" s="3">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="560" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C560" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G560" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H560" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J560" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K560" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L560" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M560" s="4">
+        <v>9799224433</v>
+      </c>
+      <c r="N560" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="R560" s="3">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="561" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C561" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G561" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H561" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J561" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K561" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L561" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M561" s="4">
+        <v>8306996024</v>
+      </c>
+      <c r="N561" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="R561" s="3">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="562" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C562" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G562" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H562" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J562" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K562" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L562" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M562" s="4">
+        <v>9414066050</v>
+      </c>
+      <c r="N562" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="R562" s="3">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="563" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C563" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G563" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H563" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J563" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K563" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L563" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M563" s="4">
+        <v>9890346405</v>
+      </c>
+      <c r="N563" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="R563" s="3">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="564" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C564" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G564" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H564" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J564" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K564" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L564" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M564" s="4">
+        <v>8005524615</v>
+      </c>
+      <c r="N564" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="R564" s="3">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="565" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C565" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G565" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="H565" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J565" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K565" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L565" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M565" s="4">
+        <v>7878229664</v>
+      </c>
+      <c r="N565" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="R565" s="3">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="566" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C566" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G566" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="H566" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J566" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K566" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L566" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M566" s="4">
+        <v>8741921477</v>
+      </c>
+      <c r="N566" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="R566" s="3">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="567" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C567" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G567" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H567" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J567" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K567" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L567" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M567" s="4">
+        <v>9696252767</v>
+      </c>
+      <c r="N567" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="R567" s="3">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="568" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C568" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G568" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H568" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J568" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="K568" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L568" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M568" s="4">
+        <v>9521890841</v>
+      </c>
+      <c r="N568" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="R568" s="3">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="569" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C569" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G569" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="H569" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J569" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K569" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L569" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M569" s="4">
+        <v>9571187498</v>
+      </c>
+      <c r="N569" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="R569" s="3">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="570" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C570" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G570" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="H570" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J570" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K570" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L570" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M570" s="4">
+        <v>9929112467</v>
+      </c>
+      <c r="N570" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="R570" s="3">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="571" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C571" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G571" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H571" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J571" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K571" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L571" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M571" s="4">
+        <v>9001199424</v>
+      </c>
+      <c r="N571" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="R571" s="3">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="572" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C572" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G572" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="H572" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J572" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K572" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L572" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M572" s="4">
+        <v>7073092072</v>
+      </c>
+      <c r="N572" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="R572" s="3">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="573" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C573" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G573" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="H573" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J573" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K573" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L573" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M573" s="4">
+        <v>9899754413</v>
+      </c>
+      <c r="N573" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="R573" s="3">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="574" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C574" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G574" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H574" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J574" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K574" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L574" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M574" s="4">
+        <v>7988083276</v>
+      </c>
+      <c r="N574" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="R574" s="3">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="575" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C575" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G575" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="H575" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J575" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K575" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L575" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M575" s="4">
+        <v>9785518369</v>
+      </c>
+      <c r="N575" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="R575" s="3">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="576" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C576" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G576" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="H576" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J576" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K576" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L576" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M576" s="4">
+        <v>8979176518</v>
+      </c>
+      <c r="N576" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="R576" s="3">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="577" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C577" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G577" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="H577" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J577" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K577" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L577" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M577" s="4">
+        <v>7085056736</v>
+      </c>
+      <c r="N577" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="R577" s="3">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="578" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C578" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G578" s="6" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H578" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J578" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K578" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L578" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M578" s="4">
+        <v>9680206141</v>
+      </c>
+      <c r="N578" s="11" t="s">
+        <v>1348</v>
+      </c>
+      <c r="R578" s="3">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="579" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C579" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="G579" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="H579" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J579" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K579" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L579" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M579" s="4">
+        <v>9928139672</v>
+      </c>
+      <c r="N579" s="11" t="s">
+        <v>1349</v>
+      </c>
+      <c r="R579" s="3">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="580" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C580" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G580" s="6" t="s">
+        <v>1335</v>
+      </c>
+      <c r="H580" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J580" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="K580" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L580" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M580" s="4">
+        <v>9414430499</v>
+      </c>
+      <c r="N580" s="11" t="s">
+        <v>1350</v>
+      </c>
+      <c r="R580" s="3">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="581" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C581" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G581" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="H581" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J581" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K581" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L581" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M581" s="4">
+        <v>8696969608</v>
+      </c>
+      <c r="N581" s="11" t="s">
+        <v>1216</v>
+      </c>
+      <c r="R581" s="3">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="582" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C582" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="G582" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="H582" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J582" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K582" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L582" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M582" s="4">
+        <v>9414075223</v>
+      </c>
+      <c r="N582" s="11" t="s">
+        <v>1217</v>
+      </c>
+      <c r="R582" s="3">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="583" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C583" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G583" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="H583" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J583" s="10" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K583" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L583" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M583" s="4">
+        <v>9251146007</v>
+      </c>
+      <c r="N583" s="11" t="s">
+        <v>1219</v>
+      </c>
+      <c r="R583" s="3">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="584" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C584" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G584" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="H584" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J584" s="10" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K584" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L584" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M584" s="4">
+        <v>9414032623</v>
+      </c>
+      <c r="N584" s="11" t="s">
+        <v>1220</v>
+      </c>
+      <c r="R584" s="3">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="585" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C585" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G585" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="H585" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J585" s="10" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K585" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L585" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M585" s="4">
+        <v>8861282015</v>
+      </c>
+      <c r="N585" s="11" t="s">
+        <v>1223</v>
+      </c>
+      <c r="R585" s="3">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="586" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C586" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G586" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="H586" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J586" s="10" t="s">
+        <v>1165</v>
+      </c>
+      <c r="K586" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L586" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M586" s="4">
+        <v>8740895928</v>
+      </c>
+      <c r="N586" s="11" t="s">
+        <v>1224</v>
+      </c>
+      <c r="R586" s="3">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="587" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C587" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="G587" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="H587" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J587" s="10" t="s">
+        <v>1165</v>
+      </c>
+      <c r="K587" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L587" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M587" s="4">
+        <v>8740895928</v>
+      </c>
+      <c r="N587" s="11" t="s">
+        <v>1220</v>
+      </c>
+      <c r="R587" s="3">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="588" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C588" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G588" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="H588" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J588" s="10" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K588" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L588" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M588" s="4">
+        <v>8861282015</v>
+      </c>
+      <c r="N588" s="11" t="s">
+        <v>1220</v>
+      </c>
+      <c r="R588" s="3">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="589" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C589" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="G589" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="H589" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J589" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K589" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L589" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M589" s="4">
+        <v>7023004000</v>
+      </c>
+      <c r="N589" s="11" t="s">
+        <v>1227</v>
+      </c>
+      <c r="R589" s="3">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="590" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C590" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G590" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="H590" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J590" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K590" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L590" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M590" s="4">
+        <v>9001195559</v>
+      </c>
+      <c r="N590" s="11" t="s">
+        <v>1228</v>
+      </c>
+      <c r="R590" s="3">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="591" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C591" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G591" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="H591" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J591" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K591" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L591" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M591" s="4">
+        <v>9829055956</v>
+      </c>
+      <c r="N591" s="11" t="s">
+        <v>1233</v>
+      </c>
+      <c r="R591" s="3">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="592" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C592" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G592" s="6" t="s">
+        <v>957</v>
+      </c>
+      <c r="H592" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J592" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K592" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L592" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M592" s="4">
+        <v>9828087828</v>
+      </c>
+      <c r="N592" s="11" t="s">
+        <v>1234</v>
+      </c>
+      <c r="R592" s="3">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="593" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C593" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G593" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="H593" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J593" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K593" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L593" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M593" s="4">
+        <v>9414020201</v>
+      </c>
+      <c r="N593" s="11" t="s">
+        <v>1236</v>
+      </c>
+      <c r="R593" s="3">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="594" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C594" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G594" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="H594" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J594" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K594" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L594" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M594" s="4">
+        <v>7976594660</v>
+      </c>
+      <c r="N594" s="11" t="s">
+        <v>1236</v>
+      </c>
+      <c r="R594" s="3">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="595" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C595" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G595" s="6" t="s">
+        <v>962</v>
+      </c>
+      <c r="H595" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J595" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K595" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L595" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M595" s="4">
+        <v>9413906890</v>
+      </c>
+      <c r="N595" s="11" t="s">
+        <v>1237</v>
+      </c>
+      <c r="R595" s="3">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="596" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C596" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G596" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="H596" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J596" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K596" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L596" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M596" s="4">
+        <v>9414326514</v>
+      </c>
+      <c r="N596" s="11" t="s">
+        <v>1238</v>
+      </c>
+      <c r="R596" s="3">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="597" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C597" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G597" s="6" t="s">
+        <v>966</v>
+      </c>
+      <c r="H597" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J597" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K597" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L597" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M597" s="4">
+        <v>9829053122</v>
+      </c>
+      <c r="N597" s="11" t="s">
+        <v>1241</v>
+      </c>
+      <c r="R597" s="3">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="598" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C598" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G598" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="H598" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J598" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K598" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L598" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M598" s="4">
+        <v>7042960810</v>
+      </c>
+      <c r="N598" s="11" t="s">
+        <v>1242</v>
+      </c>
+      <c r="R598" s="3">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="599" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C599" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G599" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="H599" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J599" s="10" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K599" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L599" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M599" s="4">
+        <v>9530400116</v>
+      </c>
+      <c r="N599" s="11" t="s">
+        <v>1245</v>
+      </c>
+      <c r="R599" s="3">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="600" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C600" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G600" s="6" t="s">
+        <v>1336</v>
+      </c>
+      <c r="H600" s="9" t="s">
+        <v>1345</v>
+      </c>
+      <c r="J600" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K600" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L600" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M600" s="4">
+        <v>9929095522</v>
+      </c>
+      <c r="N600" s="11" t="s">
+        <v>1351</v>
+      </c>
+      <c r="R600" s="3">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="601" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C601" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G601" s="6" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H601" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J601" s="10"/>
+      <c r="K601" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L601" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M601" s="4">
+        <v>9782858684</v>
+      </c>
+      <c r="N601" s="11"/>
+      <c r="R601" s="3">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="602" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C602" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G602" s="6" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H602" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J602" s="10"/>
+      <c r="K602" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L602" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M602" s="4">
+        <v>9887796804</v>
+      </c>
+      <c r="N602" s="11"/>
+      <c r="R602" s="3">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="603" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C603" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G603" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="H603" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J603" s="10"/>
+      <c r="K603" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L603" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M603" s="4">
+        <v>9461617191</v>
+      </c>
+      <c r="N603" s="11"/>
+      <c r="R603" s="3">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="604" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C604" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G604" s="6" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H604" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J604" s="10"/>
+      <c r="K604" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L604" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M604" s="4">
+        <v>9024496052</v>
+      </c>
+      <c r="N604" s="11"/>
+      <c r="R604" s="3">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="605" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C605" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G605" s="6" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H605" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J605" s="10"/>
+      <c r="K605" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L605" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M605" s="4">
+        <v>9887937443</v>
+      </c>
+      <c r="N605" s="11"/>
+      <c r="R605" s="3">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="606" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C606" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G606" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="H606" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J606" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K606" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L606" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M606" s="4">
+        <v>8952000025</v>
+      </c>
+      <c r="N606" s="11" t="s">
+        <v>1255</v>
+      </c>
+      <c r="R606" s="3">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="607" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C607" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G607" s="6" t="s">
+        <v>985</v>
+      </c>
+      <c r="H607" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J607" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K607" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L607" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M607" s="4">
+        <v>9829246123</v>
+      </c>
+      <c r="N607" s="11" t="s">
+        <v>1257</v>
+      </c>
+      <c r="R607" s="3">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="608" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C608" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G608" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="H608" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J608" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K608" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L608" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M608" s="4">
+        <v>7760045577</v>
+      </c>
+      <c r="N608" s="11" t="s">
+        <v>1259</v>
+      </c>
+      <c r="R608" s="3">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="609" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C609" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G609" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="H609" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J609" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K609" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L609" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M609" s="4">
+        <v>9829212503</v>
+      </c>
+      <c r="N609" s="11" t="s">
+        <v>1263</v>
+      </c>
+      <c r="R609" s="3">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="610" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C610" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G610" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="H610" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J610" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K610" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L610" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M610" s="4">
+        <v>9001098969</v>
+      </c>
+      <c r="N610" s="11" t="s">
+        <v>1264</v>
+      </c>
+      <c r="R610" s="3">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="611" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C611" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G611" s="6" t="s">
+        <v>997</v>
+      </c>
+      <c r="H611" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J611" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K611" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L611" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M611" s="4">
+        <v>8890141577</v>
+      </c>
+      <c r="N611" s="11" t="s">
+        <v>1268</v>
+      </c>
+      <c r="R611" s="3">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="612" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C612" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G612" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H612" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J612" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K612" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L612" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M612" s="4">
+        <v>9713776955</v>
+      </c>
+      <c r="N612" s="11" t="s">
+        <v>1273</v>
+      </c>
+      <c r="R612" s="3">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="613" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C613" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G613" s="6" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H613" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J613" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K613" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L613" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M613" s="4">
+        <v>9829137116</v>
+      </c>
+      <c r="N613" s="11" t="s">
+        <v>1274</v>
+      </c>
+      <c r="R613" s="3">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="614" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C614" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G614" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H614" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J614" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K614" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L614" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M614" s="4">
+        <v>9829010504</v>
+      </c>
+      <c r="N614" s="11" t="s">
+        <v>1279</v>
+      </c>
+      <c r="R614" s="3">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="615" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C615" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G615" s="6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H615" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J615" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K615" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L615" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M615" s="4">
+        <v>9602013918</v>
+      </c>
+      <c r="N615" s="11" t="s">
+        <v>1283</v>
+      </c>
+      <c r="R615" s="3">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="616" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C616" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G616" s="6" t="s">
+        <v>1342</v>
+      </c>
+      <c r="H616" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J616" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K616" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L616" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M616" s="4">
+        <v>9470586950</v>
+      </c>
+      <c r="N616" s="11" t="s">
+        <v>1252</v>
+      </c>
+      <c r="R616" s="3">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="617" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C617" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G617" s="6" t="s">
+        <v>1343</v>
+      </c>
+      <c r="H617" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J617" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K617" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L617" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M617" s="4">
+        <v>9460842266</v>
+      </c>
+      <c r="N617" s="11" t="s">
+        <v>1352</v>
+      </c>
+      <c r="R617" s="3">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="618" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C618" s="2">
+        <v>8</v>
+      </c>
+      <c r="G618" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="H618" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J618" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K618" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L618" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M618" s="4">
+        <v>9782371573</v>
+      </c>
+      <c r="N618" s="11" t="s">
+        <v>732</v>
+      </c>
+      <c r="R618" s="3">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="619" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C619" s="2">
+        <v>9</v>
+      </c>
+      <c r="G619" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="H619" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J619" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K619" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L619" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M619" s="4">
+        <v>8058553798</v>
+      </c>
+      <c r="N619" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="R619" s="3">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="620" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C620" s="2">
+        <v>47</v>
+      </c>
+      <c r="G620" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="H620" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J620" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K620" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L620" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M620" s="4">
+        <v>9950851729</v>
+      </c>
+      <c r="N620" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R620" s="3">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="621" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C621" s="2">
+        <v>54</v>
+      </c>
+      <c r="G621" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="H621" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J621" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="K621" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L621" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M621" s="4">
+        <v>9314167985</v>
+      </c>
+      <c r="N621" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R621" s="3">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="622" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C622" s="2">
+        <v>56</v>
+      </c>
+      <c r="G622" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="H622" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J622" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="K622" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L622" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M622" s="4">
+        <v>9610006765</v>
+      </c>
+      <c r="N622" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R622" s="3">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="623" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C623" s="2">
+        <v>57</v>
+      </c>
+      <c r="G623" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H623" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J623" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K623" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L623" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M623" s="4">
+        <v>9314646204</v>
+      </c>
+      <c r="N623" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R623" s="3">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="624" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C624" s="2">
+        <v>58</v>
+      </c>
+      <c r="G624" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="H624" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J624" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K624" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L624" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M624" s="4">
+        <v>9414088111</v>
+      </c>
+      <c r="N624" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R624" s="3">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="625" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C625" s="2">
+        <v>59</v>
+      </c>
+      <c r="G625" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="H625" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J625" s="10" t="s">
+        <v>1165</v>
+      </c>
+      <c r="K625" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L625" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M625" s="4">
+        <v>9001199281</v>
+      </c>
+      <c r="N625" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R625" s="3">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="626" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C626" s="2">
+        <v>74</v>
+      </c>
+      <c r="G626" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="H626" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J626" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K626" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L626" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M626" s="4">
+        <v>9001199209</v>
+      </c>
+      <c r="N626" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R626" s="3">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="627" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C627" s="2">
+        <v>274</v>
+      </c>
+      <c r="G627" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H627" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J627" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="K627" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L627" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M627" s="4">
+        <v>8078629190</v>
+      </c>
+      <c r="N627" s="12" t="s">
+        <v>1353</v>
+      </c>
+      <c r="R627" s="3">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="628" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C628" s="2">
+        <v>276</v>
+      </c>
+      <c r="G628" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="H628" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J628" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K628" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L628" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M628" s="5">
+        <v>9829156901</v>
+      </c>
+      <c r="N628" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R628" s="3">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="629" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C629" s="2">
+        <v>281</v>
+      </c>
+      <c r="G629" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="H629" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J629" s="10" t="s">
+        <v>1163</v>
+      </c>
+      <c r="K629" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L629" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M629" s="4">
+        <v>9530400275</v>
+      </c>
+      <c r="N629" s="11" t="s">
+        <v>1181</v>
+      </c>
+      <c r="R629" s="3">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="630" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C630" s="2">
+        <v>289</v>
+      </c>
+      <c r="G630" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="H630" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J630" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="K630" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L630" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M630" s="4">
+        <v>9571967602</v>
+      </c>
+      <c r="N630" s="11" t="s">
+        <v>1189</v>
+      </c>
+      <c r="R630" s="3">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="631" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C631" s="2">
+        <v>291</v>
+      </c>
+      <c r="G631" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="H631" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J631" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K631" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L631" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M631" s="4">
+        <v>9928906129</v>
+      </c>
+      <c r="N631" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R631" s="3">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="632" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C632" s="2">
+        <v>292</v>
+      </c>
+      <c r="G632" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="H632" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J632" s="10" t="s">
+        <v>1165</v>
+      </c>
+      <c r="K632" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L632" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M632" s="4">
+        <v>9829193377</v>
+      </c>
+      <c r="N632" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R632" s="3">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="633" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C633" s="2">
+        <v>293</v>
+      </c>
+      <c r="G633" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="H633" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J633" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="K633" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L633" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M633" s="4">
+        <v>9694678222</v>
+      </c>
+      <c r="N633" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R633" s="3">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="634" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C634" s="2">
+        <v>294</v>
+      </c>
+      <c r="G634" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="H634" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J634" s="10" t="s">
+        <v>1160</v>
+      </c>
+      <c r="K634" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L634" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M634" s="4">
+        <v>9829062608</v>
+      </c>
+      <c r="N634" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R634" s="3">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="635" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C635" s="2">
+        <v>295</v>
+      </c>
+      <c r="G635" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="H635" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J635" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="K635" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L635" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M635" s="4">
+        <v>7976417072</v>
+      </c>
+      <c r="N635" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R635" s="3">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="636" spans="3:18" x14ac:dyDescent="0.25">
+      <c r="C636" s="2">
+        <v>300</v>
+      </c>
+      <c r="G636" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="H636" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="J636" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="K636" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="L636" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M636" s="4">
+        <v>6377575455</v>
+      </c>
+      <c r="N636" s="11" t="s">
+        <v>712</v>
+      </c>
+      <c r="R636" s="3">
+        <v>2210</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N274" r:id="rId1"/>
-    <hyperlink ref="N275" r:id="rId2"/>
-    <hyperlink ref="N276" r:id="rId3"/>
-    <hyperlink ref="N277" r:id="rId4"/>
-    <hyperlink ref="N278" r:id="rId5"/>
-    <hyperlink ref="N279" r:id="rId6"/>
-    <hyperlink ref="N280" r:id="rId7"/>
-    <hyperlink ref="N281" r:id="rId8"/>
-    <hyperlink ref="N282" r:id="rId9"/>
-    <hyperlink ref="N283" r:id="rId10"/>
-    <hyperlink ref="N284" r:id="rId11"/>
-    <hyperlink ref="N289" r:id="rId12"/>
-    <hyperlink ref="N290" r:id="rId13"/>
-    <hyperlink ref="N293" r:id="rId14"/>
-    <hyperlink ref="N294" r:id="rId15"/>
-    <hyperlink ref="N295" r:id="rId16"/>
-    <hyperlink ref="N302" r:id="rId17"/>
-    <hyperlink ref="N304" r:id="rId18"/>
-    <hyperlink ref="N305" r:id="rId19"/>
-    <hyperlink ref="N306" r:id="rId20"/>
-    <hyperlink ref="N323" r:id="rId21"/>
-    <hyperlink ref="N324" r:id="rId22"/>
-    <hyperlink ref="N325" r:id="rId23"/>
-    <hyperlink ref="N326" r:id="rId24"/>
-    <hyperlink ref="N327" r:id="rId25"/>
-    <hyperlink ref="N328" r:id="rId26"/>
-    <hyperlink ref="N329" r:id="rId27"/>
-    <hyperlink ref="N430" r:id="rId28"/>
-    <hyperlink ref="N431" r:id="rId29"/>
-    <hyperlink ref="N432" r:id="rId30"/>
-    <hyperlink ref="N434" r:id="rId31"/>
-    <hyperlink ref="N435" r:id="rId32"/>
-    <hyperlink ref="N436" r:id="rId33"/>
-    <hyperlink ref="N437" r:id="rId34"/>
-    <hyperlink ref="N438" r:id="rId35"/>
-    <hyperlink ref="N439" r:id="rId36"/>
-    <hyperlink ref="N523" r:id="rId37"/>
-    <hyperlink ref="N524" r:id="rId38"/>
-    <hyperlink ref="N525" r:id="rId39"/>
+    <hyperlink ref="N274" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N275" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N276" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N277" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N278" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N279" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N280" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N281" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N282" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N283" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N284" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N289" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N290" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N293" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N294" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N295" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N302" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N304" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N305" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N306" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N323" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N324" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N325" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N326" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N327" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N328" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N329" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N430" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N431" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="N432" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="N434" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="N435" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="N436" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="N437" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="N438" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="N439" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="N523" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="N524" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="N525" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="N627" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
